--- a/data/Taller_DET_Agosto/Carga_ob_8lhds/elmo_data.xlsx
+++ b/data/Taller_DET_Agosto/Carga_ob_8lhds/elmo_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Taller_DET_Agosto\Carga_ob_8lhds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C11E2C2-93BA-4D11-B63D-65C4D6632BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC2E155-7237-44EB-8116-552BF8620E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2490,7 +2490,7 @@
         <v>5733</v>
       </c>
       <c r="F3" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G3" s="8">
         <v>1</v>
